--- a/test/project/xlsx/TestData.xlsx
+++ b/test/project/xlsx/TestData.xlsx
@@ -19,7 +19,7 @@
     <sheet name="Csv" sheetId="2" r:id="rId4"/>
     <sheet name="Tsv" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr fullCalcOnLoad="1" calcMode="auto"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="71">
   <si>
     <t>Key</t>
   </si>
@@ -203,6 +203,45 @@
   </si>
   <si>
     <t>Integers::array{integer}</t>
+  </si>
+  <si>
+    <t>1.0;2.0;3.0</t>
+  </si>
+  <si>
+    <t>4.0;5.0;6.0</t>
+  </si>
+  <si>
+    <t>7.0;8.0;9.0</t>
+  </si>
+  <si>
+    <t>10.0;11.0;12.0</t>
+  </si>
+  <si>
+    <t>13.0;14.0;15.0</t>
+  </si>
+  <si>
+    <t>/TimeZone</t>
+  </si>
+  <si>
+    <t>/Sun/Rise</t>
+  </si>
+  <si>
+    <t>/Sun/Set</t>
+  </si>
+  <si>
+    <t>/SoundProfile/MasterVolume</t>
+  </si>
+  <si>
+    <t>/SoundProfile/DialogueVolume</t>
+  </si>
+  <si>
+    <t>/ProfileSpecificGameProfile/Sensitivity</t>
+  </si>
+  <si>
+    <t>/ProfileSpecificGameProfile/Invert/x</t>
+  </si>
+  <si>
+    <t>/ProfileSpecificGameProfile/Invert/y</t>
   </si>
 </sst>
 </file>
@@ -556,10 +595,8 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="A2"/>
+      <c r="C2" t="s" s="1">
         <v>24</v>
       </c>
       <c r="D2" t="s">
@@ -567,47 +604,80 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>63</v>
+      </c>
       <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C4" s="1" t="s">
+      <c r="A4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" t="n">
+        <v>18</v>
+      </c>
       <c r="D5" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C6" s="1" t="s">
+      <c r="A6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90</v>
+      </c>
+      <c r="C6" t="s" s="1">
         <v>29</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C7" s="1" t="s">
+      <c r="A7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="s" s="1">
         <v>30</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C8" s="1" t="s">
+      <c r="A8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" t="b">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D8" t="b">
@@ -615,7 +685,13 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C9" s="1" t="s">
+      <c r="A9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" t="s" s="1">
         <v>32</v>
       </c>
       <c r="D9" t="b">
@@ -623,7 +699,13 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C10" s="1" t="s">
+      <c r="A10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" t="s" s="1">
         <v>33</v>
       </c>
       <c r="D10" t="b">
@@ -646,120 +728,120 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s" s="2">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s" s="2">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s" s="2">
         <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>50</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F2" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>10</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F3" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>15</v>
       </c>
       <c r="D4" t="s">
         <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F4" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>20</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F5" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>5</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>25</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F6" t="s">
         <v>55</v>
@@ -777,104 +859,104 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s" s="2">
         <v>13</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s" s="2">
         <v>14</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s" s="2">
         <v>15</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>50</v>
       </c>
       <c r="D2" t="s">
         <v>17</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>10</v>
       </c>
       <c r="D3" t="s">
         <v>18</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>15</v>
       </c>
       <c r="D4" t="s">
         <v>19</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>20</v>
       </c>
       <c r="D5" t="s">
         <v>20</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>5</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>25</v>
       </c>
       <c r="D6" t="s">
         <v>21</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>7</v>
       </c>
     </row>
@@ -892,27 +974,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s" s="2">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s" s="2">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s" s="2">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s" s="2">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s" s="2">
         <v>34</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s" s="2">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2">
+      <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="s">
@@ -921,7 +1003,7 @@
       <c r="D2" t="s">
         <v>4</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>50</v>
       </c>
       <c r="F2" t="s">
@@ -932,7 +1014,7 @@
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3">
+      <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="s">
@@ -941,7 +1023,7 @@
       <c r="D3" t="s">
         <v>5</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="s">
@@ -952,7 +1034,7 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4">
+      <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="s">
@@ -961,7 +1043,7 @@
       <c r="D4" t="s">
         <v>4</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>15</v>
       </c>
       <c r="F4" t="s">
@@ -972,7 +1054,7 @@
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5">
+      <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" t="s">
@@ -981,7 +1063,7 @@
       <c r="D5" t="s">
         <v>6</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>20</v>
       </c>
       <c r="F5" t="s">
@@ -992,7 +1074,7 @@
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6">
+      <c r="B6" t="n">
         <v>5</v>
       </c>
       <c r="C6" t="s">
@@ -1001,7 +1083,7 @@
       <c r="D6" t="s">
         <v>5</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>25</v>
       </c>
       <c r="F6" t="s">
@@ -1026,27 +1108,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s" s="2">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s" s="2">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s" s="2">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s" s="2">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s" s="2">
         <v>34</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s" s="2">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2">
+      <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="s">
@@ -1055,7 +1137,7 @@
       <c r="D2" t="s">
         <v>4</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>50</v>
       </c>
       <c r="F2" t="s">
@@ -1066,7 +1148,7 @@
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3">
+      <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="s">
@@ -1075,7 +1157,7 @@
       <c r="D3" t="s">
         <v>5</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="s">
@@ -1086,7 +1168,7 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4">
+      <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="s">
@@ -1095,7 +1177,7 @@
       <c r="D4" t="s">
         <v>4</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>15</v>
       </c>
       <c r="F4" t="s">
@@ -1106,7 +1188,7 @@
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5">
+      <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" t="s">
@@ -1115,7 +1197,7 @@
       <c r="D5" t="s">
         <v>6</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>20</v>
       </c>
       <c r="F5" t="s">
@@ -1126,7 +1208,7 @@
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6">
+      <c r="B6" t="n">
         <v>5</v>
       </c>
       <c r="C6" t="s">
@@ -1135,7 +1217,7 @@
       <c r="D6" t="s">
         <v>5</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>25</v>
       </c>
       <c r="F6" t="s">
